--- a/ig/DM-AVRIL-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="938">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00.000+00:00</t>
+    <t>2026-05-05T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1480,7 +1480,10 @@
     <t>236</t>
   </si>
   <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+    <t>Service de placement familial</t>
+  </si>
+  <si>
+    <t>Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
   </si>
   <si>
     <t>237</t>
@@ -5829,17 +5832,19 @@
       <c r="C207" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="D207" s="2"/>
+      <c r="D207" t="s" s="2">
+        <v>489</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
         <v>87</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5848,10 +5853,10 @@
         <v>87</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5860,10 +5865,10 @@
         <v>87</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5872,10 +5877,10 @@
         <v>87</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5884,10 +5889,10 @@
         <v>87</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5896,10 +5901,10 @@
         <v>87</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5908,10 +5913,10 @@
         <v>87</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5920,10 +5925,10 @@
         <v>87</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5932,10 +5937,10 @@
         <v>87</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5944,10 +5949,10 @@
         <v>87</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5956,10 +5961,10 @@
         <v>87</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5968,10 +5973,10 @@
         <v>87</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5980,10 +5985,10 @@
         <v>87</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5992,10 +5997,10 @@
         <v>87</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -6004,10 +6009,10 @@
         <v>87</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6016,10 +6021,10 @@
         <v>87</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6028,10 +6033,10 @@
         <v>87</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6040,10 +6045,10 @@
         <v>87</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -6052,10 +6057,10 @@
         <v>87</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -6064,10 +6069,10 @@
         <v>87</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -6076,10 +6081,10 @@
         <v>87</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -6088,10 +6093,10 @@
         <v>87</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -6100,10 +6105,10 @@
         <v>87</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -6112,10 +6117,10 @@
         <v>87</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -6124,10 +6129,10 @@
         <v>87</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -6136,10 +6141,10 @@
         <v>87</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -6148,10 +6153,10 @@
         <v>87</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -6160,10 +6165,10 @@
         <v>87</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D235" s="2"/>
     </row>
@@ -6172,10 +6177,10 @@
         <v>87</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D236" s="2"/>
     </row>
@@ -6184,10 +6189,10 @@
         <v>87</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D237" s="2"/>
     </row>
@@ -6196,10 +6201,10 @@
         <v>87</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D238" s="2"/>
     </row>
@@ -6208,10 +6213,10 @@
         <v>87</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -6220,10 +6225,10 @@
         <v>87</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D240" s="2"/>
     </row>
@@ -6232,10 +6237,10 @@
         <v>87</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -6244,10 +6249,10 @@
         <v>87</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -6256,10 +6261,10 @@
         <v>87</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -6268,10 +6273,10 @@
         <v>87</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D244" s="2"/>
     </row>
@@ -6280,10 +6285,10 @@
         <v>87</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -6292,10 +6297,10 @@
         <v>87</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D246" s="2"/>
     </row>
@@ -6304,10 +6309,10 @@
         <v>87</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -6316,10 +6321,10 @@
         <v>87</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -6328,10 +6333,10 @@
         <v>87</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -6340,10 +6345,10 @@
         <v>87</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -6352,10 +6357,10 @@
         <v>87</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -6364,10 +6369,10 @@
         <v>87</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -6376,10 +6381,10 @@
         <v>87</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -6388,10 +6393,10 @@
         <v>87</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -6400,10 +6405,10 @@
         <v>87</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -6412,10 +6417,10 @@
         <v>87</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -6424,10 +6429,10 @@
         <v>87</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -6436,10 +6441,10 @@
         <v>87</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -6448,10 +6453,10 @@
         <v>87</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -6460,10 +6465,10 @@
         <v>87</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -6472,10 +6477,10 @@
         <v>87</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -6484,10 +6489,10 @@
         <v>87</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -6496,10 +6501,10 @@
         <v>87</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -6508,10 +6513,10 @@
         <v>87</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -6520,10 +6525,10 @@
         <v>87</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -6532,10 +6537,10 @@
         <v>87</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -6544,10 +6549,10 @@
         <v>87</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -6556,10 +6561,10 @@
         <v>87</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -6568,10 +6573,10 @@
         <v>87</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -6580,10 +6585,10 @@
         <v>87</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -6592,10 +6597,10 @@
         <v>87</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -6604,10 +6609,10 @@
         <v>87</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -6616,10 +6621,10 @@
         <v>87</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -6628,10 +6633,10 @@
         <v>87</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -6640,7 +6645,7 @@
         <v>87</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C275" t="s" s="2">
         <v>201</v>
@@ -6652,10 +6657,10 @@
         <v>87</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -6664,10 +6669,10 @@
         <v>87</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -6676,10 +6681,10 @@
         <v>87</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -6688,10 +6693,10 @@
         <v>87</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -6700,10 +6705,10 @@
         <v>87</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D280" s="2"/>
     </row>
@@ -6712,10 +6717,10 @@
         <v>87</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -6724,10 +6729,10 @@
         <v>87</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D282" s="2"/>
     </row>
@@ -6736,10 +6741,10 @@
         <v>87</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D283" s="2"/>
     </row>
@@ -6748,10 +6753,10 @@
         <v>87</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -6760,10 +6765,10 @@
         <v>87</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -6772,10 +6777,10 @@
         <v>87</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -6784,10 +6789,10 @@
         <v>87</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -6796,10 +6801,10 @@
         <v>87</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -6808,10 +6813,10 @@
         <v>87</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -6820,10 +6825,10 @@
         <v>87</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -6832,10 +6837,10 @@
         <v>87</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D291" s="2"/>
     </row>
@@ -6844,10 +6849,10 @@
         <v>87</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D292" s="2"/>
     </row>
@@ -6856,10 +6861,10 @@
         <v>87</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D293" s="2"/>
     </row>
@@ -6868,10 +6873,10 @@
         <v>87</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -6880,10 +6885,10 @@
         <v>87</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -6892,10 +6897,10 @@
         <v>87</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -6904,10 +6909,10 @@
         <v>87</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -6916,10 +6921,10 @@
         <v>87</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -6928,10 +6933,10 @@
         <v>87</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -6940,10 +6945,10 @@
         <v>87</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -6952,10 +6957,10 @@
         <v>87</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -6964,10 +6969,10 @@
         <v>87</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -6976,10 +6981,10 @@
         <v>87</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D303" s="2"/>
     </row>
@@ -6988,10 +6993,10 @@
         <v>87</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -7000,10 +7005,10 @@
         <v>87</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -7012,10 +7017,10 @@
         <v>87</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -7024,10 +7029,10 @@
         <v>87</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -7036,10 +7041,10 @@
         <v>87</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -7048,10 +7053,10 @@
         <v>87</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -7060,10 +7065,10 @@
         <v>87</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7072,10 +7077,10 @@
         <v>87</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7084,10 +7089,10 @@
         <v>87</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7096,10 +7101,10 @@
         <v>87</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7108,10 +7113,10 @@
         <v>87</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7120,10 +7125,10 @@
         <v>87</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7132,10 +7137,10 @@
         <v>87</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7144,10 +7149,10 @@
         <v>87</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7156,10 +7161,10 @@
         <v>87</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7168,10 +7173,10 @@
         <v>87</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7180,10 +7185,10 @@
         <v>87</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7192,10 +7197,10 @@
         <v>87</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7204,10 +7209,10 @@
         <v>87</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7216,10 +7221,10 @@
         <v>87</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7228,10 +7233,10 @@
         <v>87</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7240,10 +7245,10 @@
         <v>87</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7252,10 +7257,10 @@
         <v>87</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7264,10 +7269,10 @@
         <v>87</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7276,10 +7281,10 @@
         <v>87</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7288,10 +7293,10 @@
         <v>87</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7300,10 +7305,10 @@
         <v>87</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7312,10 +7317,10 @@
         <v>87</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7324,10 +7329,10 @@
         <v>87</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7336,10 +7341,10 @@
         <v>87</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7348,10 +7353,10 @@
         <v>87</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7360,10 +7365,10 @@
         <v>87</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7372,10 +7377,10 @@
         <v>87</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7384,10 +7389,10 @@
         <v>87</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7396,10 +7401,10 @@
         <v>87</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7408,10 +7413,10 @@
         <v>87</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7420,10 +7425,10 @@
         <v>87</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7432,10 +7437,10 @@
         <v>87</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7444,10 +7449,10 @@
         <v>87</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7456,10 +7461,10 @@
         <v>87</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7468,10 +7473,10 @@
         <v>87</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7480,10 +7485,10 @@
         <v>87</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7492,10 +7497,10 @@
         <v>87</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7504,10 +7509,10 @@
         <v>87</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7516,10 +7521,10 @@
         <v>87</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7528,10 +7533,10 @@
         <v>87</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7540,10 +7545,10 @@
         <v>87</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7552,10 +7557,10 @@
         <v>87</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7564,10 +7569,10 @@
         <v>87</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7576,10 +7581,10 @@
         <v>87</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7588,10 +7593,10 @@
         <v>87</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7600,10 +7605,10 @@
         <v>87</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7612,10 +7617,10 @@
         <v>87</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7624,10 +7629,10 @@
         <v>87</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7636,10 +7641,10 @@
         <v>87</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7648,10 +7653,10 @@
         <v>87</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7660,10 +7665,10 @@
         <v>87</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7672,10 +7677,10 @@
         <v>87</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7684,10 +7689,10 @@
         <v>87</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7696,10 +7701,10 @@
         <v>87</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7708,10 +7713,10 @@
         <v>87</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7720,10 +7725,10 @@
         <v>87</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7732,10 +7737,10 @@
         <v>87</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7744,10 +7749,10 @@
         <v>87</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7756,10 +7761,10 @@
         <v>87</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7768,10 +7773,10 @@
         <v>87</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7780,10 +7785,10 @@
         <v>87</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7792,10 +7797,10 @@
         <v>87</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7804,10 +7809,10 @@
         <v>87</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7816,10 +7821,10 @@
         <v>87</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7828,10 +7833,10 @@
         <v>87</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7840,10 +7845,10 @@
         <v>87</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7852,10 +7857,10 @@
         <v>87</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7864,7 +7869,7 @@
         <v>87</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C377" t="s" s="2">
         <v>173</v>
@@ -7876,10 +7881,10 @@
         <v>87</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7888,13 +7893,13 @@
         <v>87</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="380">
@@ -7902,7 +7907,7 @@
         <v>87</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C380" t="s" s="2">
         <v>177</v>
@@ -7914,10 +7919,10 @@
         <v>87</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7926,10 +7931,10 @@
         <v>87</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7938,10 +7943,10 @@
         <v>87</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7950,10 +7955,10 @@
         <v>87</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7962,10 +7967,10 @@
         <v>87</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7974,10 +7979,10 @@
         <v>87</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7986,10 +7991,10 @@
         <v>87</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7998,10 +8003,10 @@
         <v>87</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -8010,7 +8015,7 @@
         <v>87</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C389" t="s" s="2">
         <v>211</v>
@@ -8022,13 +8027,13 @@
         <v>87</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D390" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="391">
@@ -8036,10 +8041,10 @@
         <v>87</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8048,10 +8053,10 @@
         <v>87</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8060,10 +8065,10 @@
         <v>87</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8072,10 +8077,10 @@
         <v>87</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8084,10 +8089,10 @@
         <v>87</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8096,10 +8101,10 @@
         <v>87</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8108,10 +8113,10 @@
         <v>87</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8120,10 +8125,10 @@
         <v>87</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8132,10 +8137,10 @@
         <v>87</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8144,10 +8149,10 @@
         <v>87</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8156,10 +8161,10 @@
         <v>87</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8168,10 +8173,10 @@
         <v>87</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8180,10 +8185,10 @@
         <v>87</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8192,10 +8197,10 @@
         <v>87</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8204,10 +8209,10 @@
         <v>87</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8216,10 +8221,10 @@
         <v>87</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8228,10 +8233,10 @@
         <v>87</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8240,10 +8245,10 @@
         <v>87</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8252,10 +8257,10 @@
         <v>87</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8264,10 +8269,10 @@
         <v>87</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8276,10 +8281,10 @@
         <v>87</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8288,10 +8293,10 @@
         <v>87</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8300,10 +8305,10 @@
         <v>87</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8312,10 +8317,10 @@
         <v>87</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8324,10 +8329,10 @@
         <v>87</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8336,10 +8341,10 @@
         <v>87</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8348,13 +8353,13 @@
         <v>87</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="418">
@@ -8362,13 +8367,13 @@
         <v>87</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D418" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="419">
@@ -8376,10 +8381,10 @@
         <v>87</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8388,10 +8393,10 @@
         <v>87</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8400,10 +8405,10 @@
         <v>87</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8412,10 +8417,10 @@
         <v>87</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8424,10 +8429,10 @@
         <v>87</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8436,10 +8441,10 @@
         <v>87</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8448,13 +8453,13 @@
         <v>87</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="426">
@@ -8462,13 +8467,13 @@
         <v>87</v>
       </c>
       <c r="B426" t="s" s="2">
+        <v>927</v>
+      </c>
+      <c r="C426" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="D426" t="s" s="2">
         <v>926</v>
-      </c>
-      <c r="C426" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="D426" t="s" s="2">
-        <v>925</v>
       </c>
     </row>
     <row r="427">
@@ -8476,13 +8481,13 @@
         <v>87</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D427" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="428">
@@ -8490,10 +8495,10 @@
         <v>87</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8502,13 +8507,13 @@
         <v>87</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D429" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="430">
@@ -8516,13 +8521,13 @@
         <v>87</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D430" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-AVRIL-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -1483,7 +1483,7 @@
     <t>Service de placement familial</t>
   </si>
   <si>
-    <t>Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
+    <t>Le placement familial est, au sens strict du terme, un dispositif qui permet de prendre en charge un enfant dans une autre famille que la sienne, afin de résoudre une situation de danger le concernant .Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
   </si>
   <si>
     <t>237</t>

--- a/ig/DM-AVRIL-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -1483,7 +1483,7 @@
     <t>Service de placement familial</t>
   </si>
   <si>
-    <t>Le placement familial est, au sens strict du terme, un dispositif qui permet de prendre en charge un enfant dans une autre famille que la sienne, afin de résoudre une situation de danger le concernant .Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
+    <t>Le placement familial est, au sens strict du terme, un dispositif qui permet de prendre en charge un enfant dans une autre famille que la sienne, afin de résoudre une situation de danger le concernant. Remarque : Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
   </si>
   <si>
     <t>237</t>
